--- a/product_surveys/006_feed_blend_support_survey--product_surveys.xlsx
+++ b/product_surveys/006_feed_blend_support_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -650,8 +650,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -679,12 +679,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sometime'}</t>
+          <t>sometime</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sometime'}</t>
+          <t>Sometime</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -730,12 +730,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -747,12 +747,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'call'}</t>
+          <t>call</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Call'}</t>
+          <t>Call</t>
         </is>
       </c>
     </row>
@@ -764,12 +764,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'message'}</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Message'}</t>
+          <t>Message</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'support_ticket'}</t>
+          <t>support_ticket</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Support Ticket'}</t>
+          <t>Support Ticket</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
